--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,1098 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128495684</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Söder om Flytarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>501209</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6760344</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128495692</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Söder om Flytarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>500939</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6760321</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128495685</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Söder om Flytarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>501198</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6760355</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128495688</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Söder om Flytarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>500933</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6760317</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128495687</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Söder om Flytarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>501180</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6760366</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128495686</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Söder om Flytarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>501190</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6760361</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128495691</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Söder om Flytarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>500881</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6760298</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128495690</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Söder om Flytarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>500905</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6760311</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128495680</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Söder om Flytarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>501205</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6760348</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppskrämd från marken</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128495689</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Söder om Flytarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>500915</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6760314</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1877,6 +1877,6710 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128624759</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>500550</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6760069</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128624790</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>500555</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6760046</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128624789</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>500562</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6760047</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128624786</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>500925</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6760280</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128624755</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>500535</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6760004</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128624756</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>500545</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6760014</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128624765</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>500690</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6760047</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128624775</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>500950</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6760227</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128624788</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>500633</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6760087</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128624785</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>500902</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6760282</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128624776</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>500965</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6760248</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128624746</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>500322</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6759809</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128624743</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>500350</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6759827</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128624767</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>500645</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6760057</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128613125</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Flytarna S om, Flytarna S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>500415</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6759913</v>
+      </c>
+      <c r="S27" t="n">
+        <v>9</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På tallraka</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128624760</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>500580</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6760099</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128624754</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>500526</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6759986</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128624781</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>500914</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6760317</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128624758</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>500550</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6760071</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128624796</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>500377</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6759937</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128624739</v>
+      </c>
+      <c r="B33" t="n">
+        <v>75171</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>500971</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6760321</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128624783</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>500892</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6760268</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128624771</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>500693</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6760153</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128624773</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>500693</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6760152</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128624797</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>500334</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6759806</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128624793</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>500417</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6759932</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128624762</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>500595</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6760109</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128624799</v>
+      </c>
+      <c r="B40" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>500888</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6760285</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128624779</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>500941</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6760321</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128624757</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>500544</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6760059</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128624741</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>500334</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6759890</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128624751</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>500415</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6759888</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128624787</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>500935</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6760276</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128624795</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>500379</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6759924</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128624777</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>500967</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6760319</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128624737</v>
+      </c>
+      <c r="B48" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>500373</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6759850</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128624798</v>
+      </c>
+      <c r="B49" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>500399</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6759852</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128624763</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>500620</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6760130</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128624778</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>500946</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6760320</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128613131</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Flytarna S om, Flytarna S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>500415</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6759913</v>
+      </c>
+      <c r="S52" t="n">
+        <v>9</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128624752</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>500425</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6759893</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128624780</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>500924</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6760317</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128624747</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>500306</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6759798</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128624749</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>500350</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6759829</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128624769</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>500660</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6760067</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128624766</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>500677</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6760057</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128613166</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Flytarna S om, Flytarna S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>500423</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6759913</v>
+      </c>
+      <c r="S59" t="n">
+        <v>9</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128624784</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>500903</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6760283</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128624753</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>500439</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6759897</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128624740</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79115</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>185</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>500925</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6760183</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128624744</v>
+      </c>
+      <c r="B63" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>500888</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6760286</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128624745</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>500334</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6759890</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128624794</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>500420</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6759913</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128624791</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>500515</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6760039</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128624748</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>500332</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6759815</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128624750</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>500394</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6759874</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128624774</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>500930</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6760194</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128624782</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>500881</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6760273</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128612798</v>
+      </c>
+      <c r="B71" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Flytarna S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>500324</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6759949</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128624792</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>500443</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6759989</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128624770</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>500638</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6760090</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128624738</v>
+      </c>
+      <c r="B74" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>500888</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6760285</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5766,32 +5766,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128624798</v>
+        <v>128624763</v>
       </c>
       <c r="B49" t="n">
-        <v>5177</v>
+        <v>79083</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>500399</v>
+        <v>500620</v>
       </c>
       <c r="R49" t="n">
-        <v>6759852</v>
+        <v>6760130</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5855,6 +5855,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5873,32 +5874,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128624763</v>
+        <v>128624798</v>
       </c>
       <c r="B50" t="n">
-        <v>79083</v>
+        <v>5177</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5908,10 +5909,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>500620</v>
+        <v>500399</v>
       </c>
       <c r="R50" t="n">
-        <v>6760130</v>
+        <v>6759852</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5943,7 +5944,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5953,7 +5954,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5962,7 +5963,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6853,7 +6853,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128613166</v>
+        <v>128624784</v>
       </c>
       <c r="B59" t="n">
         <v>79083</v>
@@ -6884,17 +6884,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Flytarna S om, Flytarna S om, Dlr</t>
+          <t>Flytarna S. om, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>500423</v>
+        <v>500903</v>
       </c>
       <c r="R59" t="n">
-        <v>6759913</v>
+        <v>6760283</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6942,6 +6942,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6960,7 +6961,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128624784</v>
+        <v>128624753</v>
       </c>
       <c r="B60" t="n">
         <v>79083</v>
@@ -6995,10 +6996,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>500903</v>
+        <v>500439</v>
       </c>
       <c r="R60" t="n">
-        <v>6760283</v>
+        <v>6759897</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7030,7 +7031,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7040,7 +7041,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7068,10 +7069,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128624753</v>
+        <v>128624740</v>
       </c>
       <c r="B61" t="n">
-        <v>79083</v>
+        <v>79115</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7079,21 +7080,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7103,10 +7104,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>500439</v>
+        <v>500925</v>
       </c>
       <c r="R61" t="n">
-        <v>6759897</v>
+        <v>6760183</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7138,7 +7139,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7148,7 +7149,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7176,10 +7177,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128624740</v>
+        <v>128613166</v>
       </c>
       <c r="B62" t="n">
-        <v>79115</v>
+        <v>79083</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7187,37 +7188,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Flytarna S. om, Dlr</t>
+          <t>Flytarna S om, Flytarna S om, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>500925</v>
+        <v>500423</v>
       </c>
       <c r="R62" t="n">
-        <v>6760183</v>
+        <v>6759913</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7246,7 +7247,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7256,7 +7257,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7265,7 +7266,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8581,6 +8581,118 @@
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128615890</v>
+      </c>
+      <c r="B75" t="n">
+        <v>43950</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Flytarna S om, Flytarna S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>500719</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6760127</v>
+      </c>
+      <c r="S75" t="n">
+        <v>9</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128495684</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128495692</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>128495685</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128495688</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>128495687</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128495686</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>128495691</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>128495690</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128495680</v>
       </c>
       <c r="B11" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>128495689</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>128624759</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>128624790</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>128624789</v>
       </c>
       <c r="B15" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128624786</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>128624755</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>128624756</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128624765</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128624775</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>128624788</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>128624785</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>128624776</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>128624746</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>128624767</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>128613125</v>
       </c>
       <c r="B27" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>128624760</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>128624754</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>128624781</v>
       </c>
       <c r="B30" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>128624758</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>128624796</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>128624739</v>
       </c>
       <c r="B33" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>128624783</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>128624771</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>128624773</v>
       </c>
       <c r="B36" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>128624793</v>
       </c>
       <c r="B38" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>128624762</v>
       </c>
       <c r="B39" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>128624779</v>
       </c>
       <c r="B41" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>128624757</v>
       </c>
       <c r="B42" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>128624741</v>
       </c>
       <c r="B43" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>128624751</v>
       </c>
       <c r="B44" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128624787</v>
       </c>
       <c r="B45" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>128624795</v>
       </c>
       <c r="B46" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128624777</v>
       </c>
       <c r="B47" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>128624763</v>
       </c>
       <c r="B49" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>128624778</v>
       </c>
       <c r="B51" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>128613131</v>
       </c>
       <c r="B52" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>128624752</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>128624780</v>
       </c>
       <c r="B54" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>128624747</v>
       </c>
       <c r="B55" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>128624749</v>
       </c>
       <c r="B56" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>128624769</v>
       </c>
       <c r="B57" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>128624766</v>
       </c>
       <c r="B58" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>128624784</v>
       </c>
       <c r="B59" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128624753</v>
       </c>
       <c r="B60" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>128624740</v>
       </c>
       <c r="B61" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>128613166</v>
       </c>
       <c r="B62" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>128624745</v>
       </c>
       <c r="B64" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>128624794</v>
       </c>
       <c r="B65" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>128624791</v>
       </c>
       <c r="B66" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>128624748</v>
       </c>
       <c r="B67" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>128624750</v>
       </c>
       <c r="B68" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>128624774</v>
       </c>
       <c r="B69" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>128624782</v>
       </c>
       <c r="B70" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>128624792</v>
       </c>
       <c r="B72" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>128624770</v>
       </c>
       <c r="B73" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>128615890</v>
       </c>
       <c r="B75" t="n">
-        <v>43950</v>
+        <v>43952</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -5123,7 +5123,7 @@
         <v>128624741</v>
       </c>
       <c r="B43" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128495684</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128495692</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>128495685</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128495688</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>128495687</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128495686</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>128495691</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>128495690</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>128495689</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>128624759</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>128624790</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>128624789</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128624786</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>128624755</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>128624756</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128624765</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128624775</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>128624788</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>128624785</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>128624776</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>128624746</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>128624767</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>128613125</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>128624760</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>128624754</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>128624781</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>128624758</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>128624796</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>128624739</v>
       </c>
       <c r="B33" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>128624783</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>128624771</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>128624773</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>128624793</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>128624762</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>128624779</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>128624757</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>128624741</v>
       </c>
       <c r="B43" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>128624751</v>
       </c>
       <c r="B44" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128624787</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>128624795</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128624777</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>128624763</v>
       </c>
       <c r="B49" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>128624778</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>128624752</v>
       </c>
       <c r="B53" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>128624780</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>128624747</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>128624749</v>
       </c>
       <c r="B56" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>128624769</v>
       </c>
       <c r="B57" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>128624766</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>128624784</v>
       </c>
       <c r="B59" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128624753</v>
       </c>
       <c r="B60" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>128624740</v>
       </c>
       <c r="B61" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>128613166</v>
       </c>
       <c r="B62" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>128624745</v>
       </c>
       <c r="B64" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>128624794</v>
       </c>
       <c r="B65" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>128624791</v>
       </c>
       <c r="B66" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>128624748</v>
       </c>
       <c r="B67" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>128624750</v>
       </c>
       <c r="B68" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>128624774</v>
       </c>
       <c r="B69" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>128624782</v>
       </c>
       <c r="B70" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>128624792</v>
       </c>
       <c r="B72" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>128624770</v>
       </c>
       <c r="B73" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -5123,7 +5123,7 @@
         <v>128624741</v>
       </c>
       <c r="B43" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128495684</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128495692</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>128495685</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128495688</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>128495687</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128495686</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>128495691</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>128495690</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128495680</v>
       </c>
       <c r="B11" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>128495689</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>128624759</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>128624790</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>128624789</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128624786</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>128624755</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>128624756</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128624765</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128624775</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>128624788</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>128624785</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>128624776</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>128624746</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>128624767</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>128613125</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>128624760</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>128624754</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>128624781</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>128624758</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>128624796</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>128624739</v>
       </c>
       <c r="B33" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>128624783</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>128624771</v>
       </c>
       <c r="B35" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>128624773</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>128624793</v>
       </c>
       <c r="B38" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>128624762</v>
       </c>
       <c r="B39" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>128624779</v>
       </c>
       <c r="B41" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>128624757</v>
       </c>
       <c r="B42" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>128624741</v>
       </c>
       <c r="B43" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>128624751</v>
       </c>
       <c r="B44" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128624787</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>128624795</v>
       </c>
       <c r="B46" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128624777</v>
       </c>
       <c r="B47" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>128624763</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>128624778</v>
       </c>
       <c r="B51" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>128613131</v>
       </c>
       <c r="B52" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>128624752</v>
       </c>
       <c r="B53" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>128624780</v>
       </c>
       <c r="B54" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>128624747</v>
       </c>
       <c r="B55" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>128624749</v>
       </c>
       <c r="B56" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>128624769</v>
       </c>
       <c r="B57" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>128624766</v>
       </c>
       <c r="B58" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>128624784</v>
       </c>
       <c r="B59" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128624753</v>
       </c>
       <c r="B60" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>128624740</v>
       </c>
       <c r="B61" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>128613166</v>
       </c>
       <c r="B62" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>128624745</v>
       </c>
       <c r="B64" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>128624794</v>
       </c>
       <c r="B65" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>128624791</v>
       </c>
       <c r="B66" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>128624748</v>
       </c>
       <c r="B67" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>128624750</v>
       </c>
       <c r="B68" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>128624774</v>
       </c>
       <c r="B69" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>128624782</v>
       </c>
       <c r="B70" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>128624792</v>
       </c>
       <c r="B72" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>128624770</v>
       </c>
       <c r="B73" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>128615890</v>
       </c>
       <c r="B75" t="n">
-        <v>43952</v>
+        <v>43979</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128495684</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128495692</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>128495685</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128495688</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>128495687</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128495686</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>128495691</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>128495690</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>128495689</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>128624759</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>128624790</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>128624789</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128624786</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>128624755</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>128624756</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128624765</v>
       </c>
       <c r="B19" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128624775</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>128624788</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>128624785</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>128624776</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>128624746</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>128624767</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>128613125</v>
       </c>
       <c r="B27" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>128624760</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>128624754</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>128624781</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>128624758</v>
       </c>
       <c r="B31" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>128624796</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>128624739</v>
       </c>
       <c r="B33" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>128624783</v>
       </c>
       <c r="B34" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>128624771</v>
       </c>
       <c r="B35" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>128624773</v>
       </c>
       <c r="B36" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>128624793</v>
       </c>
       <c r="B38" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>128624762</v>
       </c>
       <c r="B39" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>128624779</v>
       </c>
       <c r="B41" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>128624757</v>
       </c>
       <c r="B42" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>128624741</v>
       </c>
       <c r="B43" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>128624751</v>
       </c>
       <c r="B44" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128624787</v>
       </c>
       <c r="B45" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>128624795</v>
       </c>
       <c r="B46" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128624777</v>
       </c>
       <c r="B47" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>128624763</v>
       </c>
       <c r="B49" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>128624778</v>
       </c>
       <c r="B51" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>128624752</v>
       </c>
       <c r="B53" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>128624780</v>
       </c>
       <c r="B54" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>128624747</v>
       </c>
       <c r="B55" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>128624749</v>
       </c>
       <c r="B56" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>128624769</v>
       </c>
       <c r="B57" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>128624766</v>
       </c>
       <c r="B58" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>128624784</v>
       </c>
       <c r="B59" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128624753</v>
       </c>
       <c r="B60" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>128624740</v>
       </c>
       <c r="B61" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>128613166</v>
       </c>
       <c r="B62" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>128624745</v>
       </c>
       <c r="B64" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>128624794</v>
       </c>
       <c r="B65" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>128624791</v>
       </c>
       <c r="B66" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>128624748</v>
       </c>
       <c r="B67" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>128624750</v>
       </c>
       <c r="B68" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>128624774</v>
       </c>
       <c r="B69" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>128624782</v>
       </c>
       <c r="B70" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>128624792</v>
       </c>
       <c r="B72" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>128624770</v>
       </c>
       <c r="B73" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128495687</v>
+        <v>128495686</v>
       </c>
       <c r="B7" t="n">
         <v>79120</v>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501180</v>
+        <v>501190</v>
       </c>
       <c r="R7" t="n">
-        <v>6760366</v>
+        <v>6760361</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128495686</v>
+        <v>128495687</v>
       </c>
       <c r="B8" t="n">
         <v>79120</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501190</v>
+        <v>501180</v>
       </c>
       <c r="R8" t="n">
-        <v>6760361</v>
+        <v>6760366</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -5123,7 +5123,7 @@
         <v>128624741</v>
       </c>
       <c r="B43" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128495686</v>
+        <v>128495687</v>
       </c>
       <c r="B7" t="n">
         <v>79120</v>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501190</v>
+        <v>501180</v>
       </c>
       <c r="R7" t="n">
-        <v>6760361</v>
+        <v>6760366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128495687</v>
+        <v>128495686</v>
       </c>
       <c r="B8" t="n">
         <v>79120</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501180</v>
+        <v>501190</v>
       </c>
       <c r="R8" t="n">
-        <v>6760366</v>
+        <v>6760361</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1543,45 +1543,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128495690</v>
+        <v>128495680</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>56907</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Söder om Flytarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500905</v>
+        <v>501205</v>
       </c>
       <c r="R10" t="n">
-        <v>6760311</v>
+        <v>6760348</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1623,7 +1631,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Uppskrämd från marken</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,7 +1645,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1644,60 +1656,52 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128495680</v>
+        <v>128495690</v>
       </c>
       <c r="B11" t="n">
-        <v>56907</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Söder om Flytarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501205</v>
+        <v>500905</v>
       </c>
       <c r="R11" t="n">
-        <v>6760348</v>
+        <v>6760311</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,12 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Uppskrämd från marken</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,6 +1752,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128495684</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128495692</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>128495685</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128495688</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>128495687</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128495686</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>128495691</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>128495680</v>
       </c>
       <c r="B10" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128495690</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>128495689</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>128624759</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>128624790</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>128624789</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128624786</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>128624755</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>128624756</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128624765</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128624775</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>128624788</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>128624785</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>128624776</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>128624746</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>128624767</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>128613125</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>128624760</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>128624754</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>128624781</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>128624758</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>128624796</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>128624739</v>
       </c>
       <c r="B33" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>128624783</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>128624771</v>
       </c>
       <c r="B35" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>128624773</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>128624793</v>
       </c>
       <c r="B38" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>128624762</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>128624779</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>128624757</v>
       </c>
       <c r="B42" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>128624741</v>
       </c>
       <c r="B43" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>128624751</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128624787</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>128624795</v>
       </c>
       <c r="B46" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128624777</v>
       </c>
       <c r="B47" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>128624763</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>128624778</v>
       </c>
       <c r="B51" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>128613131</v>
       </c>
       <c r="B52" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>128624752</v>
       </c>
       <c r="B53" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>128624780</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>128624747</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>128624749</v>
       </c>
       <c r="B56" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>128624769</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>128624766</v>
       </c>
       <c r="B58" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>128624784</v>
       </c>
       <c r="B59" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128624753</v>
       </c>
       <c r="B60" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>128624740</v>
       </c>
       <c r="B61" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>128613166</v>
       </c>
       <c r="B62" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>128624745</v>
       </c>
       <c r="B64" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>128624794</v>
       </c>
       <c r="B65" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>128624791</v>
       </c>
       <c r="B66" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>128624748</v>
       </c>
       <c r="B67" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>128624750</v>
       </c>
       <c r="B68" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>128624774</v>
       </c>
       <c r="B69" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>128624782</v>
       </c>
       <c r="B70" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>128624792</v>
       </c>
       <c r="B72" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>128624770</v>
       </c>
       <c r="B73" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>128615890</v>
       </c>
       <c r="B75" t="n">
-        <v>43979</v>
+        <v>43980</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -1543,53 +1543,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128495680</v>
+        <v>128495690</v>
       </c>
       <c r="B10" t="n">
-        <v>56910</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Söder om Flytarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501205</v>
+        <v>500905</v>
       </c>
       <c r="R10" t="n">
-        <v>6760348</v>
+        <v>6760311</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,7 +1613,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,12 +1623,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Uppskrämd från marken</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,6 +1632,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1656,52 +1644,60 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128495690</v>
+        <v>128495680</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>56910</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Söder om Flytarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500905</v>
+        <v>501205</v>
       </c>
       <c r="R11" t="n">
-        <v>6760311</v>
+        <v>6760348</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1729,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1739,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppskrämd från marken</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,7 +1753,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128495684</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128495692</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>128495685</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128495688</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>128495687</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128495686</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>128495691</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,45 +1543,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128495690</v>
+        <v>128495680</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>56913</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Söder om Flytarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500905</v>
+        <v>501205</v>
       </c>
       <c r="R10" t="n">
-        <v>6760311</v>
+        <v>6760348</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1623,7 +1631,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Uppskrämd från marken</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,7 +1645,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1644,60 +1656,52 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128495680</v>
+        <v>128495690</v>
       </c>
       <c r="B11" t="n">
-        <v>56910</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Söder om Flytarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501205</v>
+        <v>500905</v>
       </c>
       <c r="R11" t="n">
-        <v>6760348</v>
+        <v>6760311</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,12 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Uppskrämd från marken</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,6 +1752,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1774,7 +1774,7 @@
         <v>128495689</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>128624759</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>128624790</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>128624789</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128624786</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>128624755</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>128624756</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128624765</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128624775</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>128624788</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>128624785</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>128624776</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>128624746</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>128624767</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>128613125</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>128624760</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>128624754</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>128624781</v>
       </c>
       <c r="B30" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>128624758</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>128624796</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>128624739</v>
       </c>
       <c r="B33" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>128624783</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>128624771</v>
       </c>
       <c r="B35" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>128624773</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>128624793</v>
       </c>
       <c r="B38" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>128624762</v>
       </c>
       <c r="B39" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>128624779</v>
       </c>
       <c r="B41" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>128624757</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>128624741</v>
       </c>
       <c r="B43" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>128624751</v>
       </c>
       <c r="B44" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128624787</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>128624795</v>
       </c>
       <c r="B46" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128624777</v>
       </c>
       <c r="B47" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>128624763</v>
       </c>
       <c r="B49" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>128624778</v>
       </c>
       <c r="B51" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>128613131</v>
       </c>
       <c r="B52" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>128624752</v>
       </c>
       <c r="B53" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>128624780</v>
       </c>
       <c r="B54" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>128624747</v>
       </c>
       <c r="B55" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>128624749</v>
       </c>
       <c r="B56" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>128624769</v>
       </c>
       <c r="B57" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>128624766</v>
       </c>
       <c r="B58" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>128624784</v>
       </c>
       <c r="B59" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128624753</v>
       </c>
       <c r="B60" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>128624740</v>
       </c>
       <c r="B61" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>128613166</v>
       </c>
       <c r="B62" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>128624745</v>
       </c>
       <c r="B64" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>128624794</v>
       </c>
       <c r="B65" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>128624791</v>
       </c>
       <c r="B66" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>128624748</v>
       </c>
       <c r="B67" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>128624750</v>
       </c>
       <c r="B68" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>128624774</v>
       </c>
       <c r="B69" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>128624782</v>
       </c>
       <c r="B70" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>128624792</v>
       </c>
       <c r="B72" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>128624770</v>
       </c>
       <c r="B73" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>128615890</v>
       </c>
       <c r="B75" t="n">
-        <v>43980</v>
+        <v>43982</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128495684</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128495692</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>128495685</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128495688</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>128495687</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128495686</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>128495691</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128495690</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>128495689</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>128624759</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>128624790</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>128624789</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128624786</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>128624755</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>128624756</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128624765</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128624775</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>128624788</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>128624785</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>128624776</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>128624746</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>128624767</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>128613125</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>128624760</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>128624754</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>128624781</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>128624758</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>128624796</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>128624739</v>
       </c>
       <c r="B33" t="n">
-        <v>83005</v>
+        <v>83010</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>128624783</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>128624771</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>128624773</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>128624793</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>128624762</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>128624779</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>128624757</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>128624741</v>
       </c>
       <c r="B43" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>128624751</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128624787</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>128624795</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128624777</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>128624763</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>128624778</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>128624752</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>128624780</v>
       </c>
       <c r="B54" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>128624747</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>128624749</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>128624769</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>128624766</v>
       </c>
       <c r="B58" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>128624784</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128624753</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>128624740</v>
       </c>
       <c r="B61" t="n">
-        <v>79061</v>
+        <v>79066</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>128613166</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>128624745</v>
       </c>
       <c r="B64" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>128624794</v>
       </c>
       <c r="B65" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>128624791</v>
       </c>
       <c r="B66" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>128624748</v>
       </c>
       <c r="B67" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>128624750</v>
       </c>
       <c r="B68" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>128624774</v>
       </c>
       <c r="B69" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>128624782</v>
       </c>
       <c r="B70" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>128624792</v>
       </c>
       <c r="B72" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>128624770</v>
       </c>
       <c r="B73" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -1882,7 +1882,7 @@
         <v>128624759</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>128624790</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>128624789</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128624786</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>128624755</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>128624756</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128624765</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128624775</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>128624788</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>128624785</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>128624776</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>128624746</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>128624767</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>128613125</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>128624760</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>128624754</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>128624781</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>128624758</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>128624796</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>128624739</v>
       </c>
       <c r="B33" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>128624783</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>128624771</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>128624773</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>128624793</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>128624762</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>128624779</v>
       </c>
       <c r="B41" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>128624757</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>128624741</v>
       </c>
       <c r="B43" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>128624751</v>
       </c>
       <c r="B44" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>128624787</v>
       </c>
       <c r="B45" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>128624795</v>
       </c>
       <c r="B46" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128624777</v>
       </c>
       <c r="B47" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>128624763</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>128624778</v>
       </c>
       <c r="B51" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>128624752</v>
       </c>
       <c r="B53" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>128624780</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>128624747</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>128624749</v>
       </c>
       <c r="B56" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>128624769</v>
       </c>
       <c r="B57" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>128624766</v>
       </c>
       <c r="B58" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>128624784</v>
       </c>
       <c r="B59" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128624753</v>
       </c>
       <c r="B60" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>128624740</v>
       </c>
       <c r="B61" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>128613166</v>
       </c>
       <c r="B62" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>128624745</v>
       </c>
       <c r="B64" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>128624794</v>
       </c>
       <c r="B65" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>128624791</v>
       </c>
       <c r="B66" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>128624748</v>
       </c>
       <c r="B67" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>128624750</v>
       </c>
       <c r="B68" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>128624774</v>
       </c>
       <c r="B69" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>128624782</v>
       </c>
       <c r="B70" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>128624792</v>
       </c>
       <c r="B72" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>128624770</v>
       </c>
       <c r="B73" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -7156,7 +7156,7 @@
         <v>0</v>
       </c>
       <c r="AE61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>77629038</v>
+        <v>128624740</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flytarna, Dlr</t>
+          <t>Flytarna S. om, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501078.2060481972</v>
+        <v>500925</v>
       </c>
       <c r="R2" t="n">
-        <v>6760348.991634858</v>
+        <v>6760183</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,52 +740,53 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-02-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-02-12</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128495684</v>
+        <v>128624741</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +794,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söder om Flytarna, Dlr</t>
+          <t>Flytarna S. om, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501209</v>
+        <v>500334</v>
       </c>
       <c r="R3" t="n">
-        <v>6760344</v>
+        <v>6759890</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,22 +848,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,29 +872,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128495692</v>
+        <v>77629038</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,34 +901,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söder om Flytarna, Dlr</t>
+          <t>Flytarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500939</v>
+        <v>501078</v>
       </c>
       <c r="R4" t="n">
-        <v>6760321</v>
+        <v>6760349</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,22 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:59</t>
+          <t>2019-02-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:59</t>
+          <t>2019-02-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,33 +969,32 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128495685</v>
+        <v>128495684</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1038,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501198</v>
+        <v>501209</v>
       </c>
       <c r="R5" t="n">
-        <v>6760355</v>
+        <v>6760344</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,7 +1057,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1083,7 +1067,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,14 +1095,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128495688</v>
+        <v>128495685</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1146,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500933</v>
+        <v>501198</v>
       </c>
       <c r="R6" t="n">
-        <v>6760317</v>
+        <v>6760355</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1165,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1175,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,14 +1203,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128495687</v>
+        <v>128495686</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1254,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501180</v>
+        <v>501190</v>
       </c>
       <c r="R7" t="n">
-        <v>6760366</v>
+        <v>6760361</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,14 +1311,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128495686</v>
+        <v>128495687</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1362,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501190</v>
+        <v>501180</v>
       </c>
       <c r="R8" t="n">
-        <v>6760361</v>
+        <v>6760366</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,14 +1419,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128495691</v>
+        <v>128495688</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1470,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500881</v>
+        <v>500933</v>
       </c>
       <c r="R9" t="n">
-        <v>6760298</v>
+        <v>6760317</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,7 +1489,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1515,7 +1499,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,53 +1527,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128495680</v>
+        <v>128495689</v>
       </c>
       <c r="B10" t="n">
-        <v>56913</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Söder om Flytarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501205</v>
+        <v>500915</v>
       </c>
       <c r="R10" t="n">
-        <v>6760348</v>
+        <v>6760314</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,7 +1597,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,12 +1607,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Uppskrämd från marken</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,6 +1616,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1656,7 +1628,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1666,11 +1638,11 @@
         <v>128495690</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1771,14 +1743,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128495689</v>
+        <v>128495691</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1806,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500915</v>
+        <v>500881</v>
       </c>
       <c r="R12" t="n">
-        <v>6760314</v>
+        <v>6760298</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1813,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1823,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1879,14 +1851,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128624759</v>
+        <v>128495692</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1910,14 +1882,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flytarna S. om, Dlr</t>
+          <t>Söder om Flytarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500550</v>
+        <v>500939</v>
       </c>
       <c r="R13" t="n">
-        <v>6760069</v>
+        <v>6760321</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,22 +1916,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,26 +1947,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128624790</v>
+        <v>128613125</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2018,17 +1990,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flytarna S. om, Dlr</t>
+          <t>Flytarna S om, Flytarna S om, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500555</v>
+        <v>500415</v>
       </c>
       <c r="R14" t="n">
-        <v>6760046</v>
+        <v>6759913</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2057,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2067,7 +2039,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På tallraka</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,7 +2053,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2095,14 +2071,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128624789</v>
+        <v>128613166</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2126,17 +2102,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flytarna S. om, Dlr</t>
+          <t>Flytarna S om, Flytarna S om, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500562</v>
+        <v>500423</v>
       </c>
       <c r="R15" t="n">
-        <v>6760047</v>
+        <v>6759913</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2165,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,7 +2160,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2203,14 +2178,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128624786</v>
+        <v>128624745</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2238,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500925</v>
+        <v>500334</v>
       </c>
       <c r="R16" t="n">
-        <v>6760280</v>
+        <v>6759890</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2311,14 +2286,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128624755</v>
+        <v>128624746</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2346,10 +2321,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500535</v>
+        <v>500322</v>
       </c>
       <c r="R17" t="n">
-        <v>6760004</v>
+        <v>6759809</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,7 +2356,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2391,7 +2366,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2419,14 +2394,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128624756</v>
+        <v>128624747</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2454,10 +2429,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500545</v>
+        <v>500306</v>
       </c>
       <c r="R18" t="n">
-        <v>6760014</v>
+        <v>6759798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,7 +2464,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2499,7 +2474,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2527,14 +2502,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128624765</v>
+        <v>128624748</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2562,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500690</v>
+        <v>500332</v>
       </c>
       <c r="R19" t="n">
-        <v>6760047</v>
+        <v>6759815</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2597,7 +2572,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2607,7 +2582,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,14 +2610,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128624775</v>
+        <v>128624749</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2670,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500950</v>
+        <v>500350</v>
       </c>
       <c r="R20" t="n">
-        <v>6760227</v>
+        <v>6759829</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,7 +2680,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2715,7 +2690,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2743,14 +2718,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128624788</v>
+        <v>128624750</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2778,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500633</v>
+        <v>500394</v>
       </c>
       <c r="R21" t="n">
-        <v>6760087</v>
+        <v>6759874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2813,7 +2788,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2823,7 +2798,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,14 +2826,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128624785</v>
+        <v>128624751</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2886,10 +2861,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500902</v>
+        <v>500415</v>
       </c>
       <c r="R22" t="n">
-        <v>6760282</v>
+        <v>6759888</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2921,7 +2896,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2931,7 +2906,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2959,14 +2934,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128624776</v>
+        <v>128624752</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2994,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500965</v>
+        <v>500425</v>
       </c>
       <c r="R23" t="n">
-        <v>6760248</v>
+        <v>6759893</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,7 +3004,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3039,7 +3014,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3067,14 +3042,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128624746</v>
+        <v>128624753</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3102,10 +3077,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500322</v>
+        <v>500439</v>
       </c>
       <c r="R24" t="n">
-        <v>6759809</v>
+        <v>6759897</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3137,7 +3112,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3147,7 +3122,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3175,32 +3150,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128624743</v>
+        <v>128624754</v>
       </c>
       <c r="B25" t="n">
-        <v>4773</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3210,10 +3185,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500350</v>
+        <v>500526</v>
       </c>
       <c r="R25" t="n">
-        <v>6759827</v>
+        <v>6759986</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3245,7 +3220,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3255,7 +3230,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3283,14 +3258,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128624767</v>
+        <v>128624755</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3318,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500645</v>
+        <v>500535</v>
       </c>
       <c r="R26" t="n">
-        <v>6760057</v>
+        <v>6760004</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3353,7 +3328,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3363,7 +3338,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3391,14 +3366,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128613125</v>
+        <v>128624756</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3422,17 +3397,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Flytarna S om, Flytarna S om, Dlr</t>
+          <t>Flytarna S. om, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500415</v>
+        <v>500545</v>
       </c>
       <c r="R27" t="n">
-        <v>6759913</v>
+        <v>6760014</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3461,7 +3436,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3471,12 +3446,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På tallraka</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3485,6 +3455,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3503,14 +3474,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128624760</v>
+        <v>128624757</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3538,10 +3509,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500580</v>
+        <v>500544</v>
       </c>
       <c r="R28" t="n">
-        <v>6760099</v>
+        <v>6760059</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,7 +3544,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3583,7 +3554,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3611,14 +3582,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128624754</v>
+        <v>128624758</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3646,10 +3617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500526</v>
+        <v>500550</v>
       </c>
       <c r="R29" t="n">
-        <v>6759986</v>
+        <v>6760071</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3681,7 +3652,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3691,7 +3662,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3719,14 +3690,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128624781</v>
+        <v>128624759</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3754,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500914</v>
+        <v>500550</v>
       </c>
       <c r="R30" t="n">
-        <v>6760317</v>
+        <v>6760069</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3789,7 +3760,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3799,7 +3770,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3827,14 +3798,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128624758</v>
+        <v>128624760</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3862,10 +3833,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500550</v>
+        <v>500580</v>
       </c>
       <c r="R31" t="n">
-        <v>6760071</v>
+        <v>6760099</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3897,7 +3868,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3907,7 +3878,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3935,14 +3906,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128624796</v>
+        <v>128624762</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3970,10 +3941,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500377</v>
+        <v>500595</v>
       </c>
       <c r="R32" t="n">
-        <v>6759937</v>
+        <v>6760109</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,7 +3976,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4015,7 +3986,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4043,32 +4014,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128624739</v>
+        <v>128624763</v>
       </c>
       <c r="B33" t="n">
-        <v>83011</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4078,10 +4049,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500971</v>
+        <v>500620</v>
       </c>
       <c r="R33" t="n">
-        <v>6760321</v>
+        <v>6760130</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4113,7 +4084,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4123,7 +4094,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4132,6 +4103,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4150,14 +4122,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128624783</v>
+        <v>128624764</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4185,10 +4157,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500892</v>
+        <v>500763</v>
       </c>
       <c r="R34" t="n">
-        <v>6760268</v>
+        <v>6760044</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4220,7 +4192,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4230,7 +4202,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4258,14 +4230,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128624771</v>
+        <v>128624765</v>
       </c>
       <c r="B35" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4293,10 +4265,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500693</v>
+        <v>500690</v>
       </c>
       <c r="R35" t="n">
-        <v>6760153</v>
+        <v>6760047</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4328,7 +4300,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4338,7 +4310,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4366,14 +4338,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128624773</v>
+        <v>128624766</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4401,10 +4373,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500693</v>
+        <v>500677</v>
       </c>
       <c r="R36" t="n">
-        <v>6760152</v>
+        <v>6760057</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4436,7 +4408,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4446,7 +4418,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4474,32 +4446,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128624797</v>
+        <v>128624767</v>
       </c>
       <c r="B37" t="n">
-        <v>5177</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4509,10 +4481,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500334</v>
+        <v>500645</v>
       </c>
       <c r="R37" t="n">
-        <v>6759806</v>
+        <v>6760057</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4544,7 +4516,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4554,7 +4526,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4563,6 +4535,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4581,14 +4554,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128624793</v>
+        <v>128624769</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4616,10 +4589,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500417</v>
+        <v>500660</v>
       </c>
       <c r="R38" t="n">
-        <v>6759932</v>
+        <v>6760067</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4651,7 +4624,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4661,7 +4634,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4689,14 +4662,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128624762</v>
+        <v>128624770</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4724,10 +4697,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500595</v>
+        <v>500638</v>
       </c>
       <c r="R39" t="n">
-        <v>6760109</v>
+        <v>6760090</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4759,7 +4732,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4769,7 +4742,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4797,32 +4770,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128624799</v>
+        <v>128624771</v>
       </c>
       <c r="B40" t="n">
-        <v>5177</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4832,10 +4805,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500888</v>
+        <v>500693</v>
       </c>
       <c r="R40" t="n">
-        <v>6760285</v>
+        <v>6760153</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4867,7 +4840,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4877,7 +4850,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4886,6 +4859,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4904,14 +4878,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128624779</v>
+        <v>128624773</v>
       </c>
       <c r="B41" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4939,10 +4913,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>500941</v>
+        <v>500693</v>
       </c>
       <c r="R41" t="n">
-        <v>6760321</v>
+        <v>6760152</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4974,7 +4948,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4984,7 +4958,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5012,14 +4986,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128624757</v>
+        <v>128624774</v>
       </c>
       <c r="B42" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5047,10 +5021,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>500544</v>
+        <v>500930</v>
       </c>
       <c r="R42" t="n">
-        <v>6760059</v>
+        <v>6760194</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5082,7 +5056,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5092,7 +5066,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5120,32 +5094,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128624741</v>
+        <v>128624775</v>
       </c>
       <c r="B43" t="n">
-        <v>91526</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5155,10 +5129,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>500334</v>
+        <v>500950</v>
       </c>
       <c r="R43" t="n">
-        <v>6759890</v>
+        <v>6760227</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5190,7 +5164,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5200,7 +5174,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5209,6 +5183,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5227,14 +5202,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128624751</v>
+        <v>128624776</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5262,10 +5237,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>500415</v>
+        <v>500965</v>
       </c>
       <c r="R44" t="n">
-        <v>6759888</v>
+        <v>6760248</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5297,7 +5272,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5307,7 +5282,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5335,14 +5310,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128624787</v>
+        <v>128624777</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5370,10 +5345,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>500935</v>
+        <v>500967</v>
       </c>
       <c r="R45" t="n">
-        <v>6760276</v>
+        <v>6760319</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5405,7 +5380,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5415,7 +5390,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,14 +5418,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128624795</v>
+        <v>128624778</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5478,10 +5453,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>500379</v>
+        <v>500946</v>
       </c>
       <c r="R46" t="n">
-        <v>6759924</v>
+        <v>6760320</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5513,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5551,14 +5526,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128624777</v>
+        <v>128624779</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5586,10 +5561,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>500967</v>
+        <v>500941</v>
       </c>
       <c r="R47" t="n">
-        <v>6760319</v>
+        <v>6760321</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5621,7 +5596,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5631,7 +5606,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5659,32 +5634,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128624737</v>
+        <v>128624780</v>
       </c>
       <c r="B48" t="n">
-        <v>5197</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5694,10 +5669,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>500373</v>
+        <v>500924</v>
       </c>
       <c r="R48" t="n">
-        <v>6759850</v>
+        <v>6760317</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5729,7 +5704,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5739,7 +5714,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5748,6 +5723,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5766,14 +5742,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128624763</v>
+        <v>128624781</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5801,10 +5777,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>500620</v>
+        <v>500914</v>
       </c>
       <c r="R49" t="n">
-        <v>6760130</v>
+        <v>6760317</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5836,7 +5812,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5846,7 +5822,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5874,32 +5850,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128624798</v>
+        <v>128624782</v>
       </c>
       <c r="B50" t="n">
-        <v>5177</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5909,10 +5885,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>500399</v>
+        <v>500881</v>
       </c>
       <c r="R50" t="n">
-        <v>6759852</v>
+        <v>6760273</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5944,7 +5920,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5954,7 +5930,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5963,6 +5939,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5981,14 +5958,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128624778</v>
+        <v>128624783</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -6016,10 +5993,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>500946</v>
+        <v>500892</v>
       </c>
       <c r="R51" t="n">
-        <v>6760320</v>
+        <v>6760268</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6051,7 +6028,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6061,7 +6038,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6089,57 +6066,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128613131</v>
+        <v>128624784</v>
       </c>
       <c r="B52" t="n">
-        <v>57883</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Flytarna S om, Flytarna S om, Dlr</t>
+          <t>Flytarna S. om, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>500415</v>
+        <v>500903</v>
       </c>
       <c r="R52" t="n">
-        <v>6759913</v>
+        <v>6760283</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6168,7 +6136,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6178,7 +6146,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6187,6 +6155,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6205,14 +6174,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128624752</v>
+        <v>128624785</v>
       </c>
       <c r="B53" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6240,10 +6209,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>500425</v>
+        <v>500902</v>
       </c>
       <c r="R53" t="n">
-        <v>6759893</v>
+        <v>6760282</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6275,7 +6244,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6285,7 +6254,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6313,14 +6282,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128624780</v>
+        <v>128624786</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6348,10 +6317,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>500924</v>
+        <v>500925</v>
       </c>
       <c r="R54" t="n">
-        <v>6760317</v>
+        <v>6760280</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6383,7 +6352,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6393,7 +6362,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6421,14 +6390,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128624747</v>
+        <v>128624787</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6456,10 +6425,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>500306</v>
+        <v>500935</v>
       </c>
       <c r="R55" t="n">
-        <v>6759798</v>
+        <v>6760276</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6491,7 +6460,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6501,7 +6470,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6529,14 +6498,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128624749</v>
+        <v>128624788</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6564,10 +6533,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>500350</v>
+        <v>500633</v>
       </c>
       <c r="R56" t="n">
-        <v>6759829</v>
+        <v>6760087</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6599,7 +6568,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6609,7 +6578,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6637,14 +6606,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128624769</v>
+        <v>128624789</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6672,10 +6641,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>500660</v>
+        <v>500562</v>
       </c>
       <c r="R57" t="n">
-        <v>6760067</v>
+        <v>6760047</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6707,7 +6676,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6717,7 +6686,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6745,14 +6714,14 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128624766</v>
+        <v>128624790</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -6780,10 +6749,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>500677</v>
+        <v>500555</v>
       </c>
       <c r="R58" t="n">
-        <v>6760057</v>
+        <v>6760046</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6815,7 +6784,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6825,7 +6794,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6853,14 +6822,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128624784</v>
+        <v>128624791</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -6888,10 +6857,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>500903</v>
+        <v>500515</v>
       </c>
       <c r="R59" t="n">
-        <v>6760283</v>
+        <v>6760039</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6923,7 +6892,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6933,7 +6902,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6961,14 +6930,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128624753</v>
+        <v>128624792</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -6996,10 +6965,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>500439</v>
+        <v>500443</v>
       </c>
       <c r="R60" t="n">
-        <v>6759897</v>
+        <v>6759989</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7031,7 +7000,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7041,7 +7010,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7069,32 +7038,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128624740</v>
+        <v>128624793</v>
       </c>
       <c r="B61" t="n">
-        <v>79067</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7104,10 +7073,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>500925</v>
+        <v>500417</v>
       </c>
       <c r="R61" t="n">
-        <v>6760183</v>
+        <v>6759932</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7139,7 +7108,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7149,14 +7118,14 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
@@ -7177,14 +7146,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128613166</v>
+        <v>128624794</v>
       </c>
       <c r="B62" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -7208,17 +7177,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Flytarna S om, Flytarna S om, Dlr</t>
+          <t>Flytarna S. om, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>500423</v>
+        <v>500420</v>
       </c>
       <c r="R62" t="n">
         <v>6759913</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7247,7 +7216,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7257,7 +7226,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7266,6 +7235,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7284,32 +7254,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128624744</v>
+        <v>128624795</v>
       </c>
       <c r="B63" t="n">
-        <v>4773</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7319,10 +7289,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>500888</v>
+        <v>500379</v>
       </c>
       <c r="R63" t="n">
-        <v>6760286</v>
+        <v>6759924</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7354,7 +7324,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7364,7 +7334,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7392,14 +7362,14 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128624745</v>
+        <v>128624796</v>
       </c>
       <c r="B64" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -7427,10 +7397,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>500334</v>
+        <v>500377</v>
       </c>
       <c r="R64" t="n">
-        <v>6759890</v>
+        <v>6759937</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7462,7 +7432,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7472,7 +7442,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7500,14 +7470,14 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128624794</v>
+        <v>128625716</v>
       </c>
       <c r="B65" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -7531,14 +7501,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Flytarna S. om, Dlr</t>
+          <t>Tövåsen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>500420</v>
+        <v>501125</v>
       </c>
       <c r="R65" t="n">
-        <v>6759913</v>
+        <v>6760280</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7570,7 +7540,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7580,7 +7550,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7596,22 +7566,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128624791</v>
+        <v>128624739</v>
       </c>
       <c r="B66" t="n">
-        <v>79035</v>
+        <v>83307</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7619,21 +7589,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7643,10 +7613,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>500515</v>
+        <v>500971</v>
       </c>
       <c r="R66" t="n">
-        <v>6760039</v>
+        <v>6760321</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7678,7 +7648,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7688,7 +7658,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7697,7 +7667,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7716,45 +7685,53 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128624748</v>
+        <v>128495680</v>
       </c>
       <c r="B67" t="n">
-        <v>79035</v>
+        <v>57141</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Flytarna S. om, Dlr</t>
+          <t>Söder om Flytarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>500332</v>
+        <v>501205</v>
       </c>
       <c r="R67" t="n">
-        <v>6759815</v>
+        <v>6760348</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7781,22 +7758,27 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Uppskrämd från marken</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7805,64 +7787,68 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128624750</v>
+        <v>128612798</v>
       </c>
       <c r="B68" t="n">
-        <v>79035</v>
+        <v>4775</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Flytarna S. om, Dlr</t>
+          <t>Flytarna S om, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>500394</v>
+        <v>500324</v>
       </c>
       <c r="R68" t="n">
-        <v>6759874</v>
+        <v>6759949</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7894,7 +7880,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7904,7 +7890,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7913,7 +7899,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7932,32 +7917,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128624774</v>
+        <v>128624743</v>
       </c>
       <c r="B69" t="n">
-        <v>79035</v>
+        <v>4775</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7967,10 +7952,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>500930</v>
+        <v>500350</v>
       </c>
       <c r="R69" t="n">
-        <v>6760194</v>
+        <v>6759827</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8002,7 +7987,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8012,7 +7997,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8040,32 +8025,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128624782</v>
+        <v>128624744</v>
       </c>
       <c r="B70" t="n">
-        <v>79035</v>
+        <v>4775</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8075,10 +8060,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>500881</v>
+        <v>500888</v>
       </c>
       <c r="R70" t="n">
-        <v>6760273</v>
+        <v>6760286</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8110,7 +8095,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8120,7 +8105,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8148,10 +8133,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128612798</v>
+        <v>128624797</v>
       </c>
       <c r="B71" t="n">
-        <v>4773</v>
+        <v>5179</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8159,39 +8144,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Flytarna S om, Dlr</t>
+          <t>Flytarna S. om, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>500324</v>
+        <v>500334</v>
       </c>
       <c r="R71" t="n">
-        <v>6759949</v>
+        <v>6759806</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8223,7 +8203,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8233,7 +8213,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8260,32 +8240,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128624792</v>
+        <v>128624798</v>
       </c>
       <c r="B72" t="n">
-        <v>79035</v>
+        <v>5179</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8295,10 +8275,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>500443</v>
+        <v>500399</v>
       </c>
       <c r="R72" t="n">
-        <v>6759989</v>
+        <v>6759852</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8330,7 +8310,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8340,7 +8320,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8349,7 +8329,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8368,32 +8347,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128624770</v>
+        <v>128624799</v>
       </c>
       <c r="B73" t="n">
-        <v>79035</v>
+        <v>5179</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8403,10 +8382,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>500638</v>
+        <v>500888</v>
       </c>
       <c r="R73" t="n">
-        <v>6760090</v>
+        <v>6760285</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8438,7 +8417,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8448,7 +8427,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8457,7 +8436,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8476,10 +8454,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128624738</v>
+        <v>128615890</v>
       </c>
       <c r="B74" t="n">
-        <v>5197</v>
+        <v>44177</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8487,37 +8465,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>105930</v>
+        <v>101735</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Flytarna S. om, Dlr</t>
+          <t>Flytarna S om, Flytarna S om, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>500888</v>
+        <v>500719</v>
       </c>
       <c r="R74" t="n">
-        <v>6760285</v>
+        <v>6760127</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8546,7 +8529,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8556,7 +8539,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8583,38 +8566,42 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128615890</v>
+        <v>128613131</v>
       </c>
       <c r="B75" t="n">
-        <v>43982</v>
+        <v>58114</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>101735</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8623,10 +8610,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>500719</v>
+        <v>500415</v>
       </c>
       <c r="R75" t="n">
-        <v>6760127</v>
+        <v>6759913</v>
       </c>
       <c r="S75" t="n">
         <v>9</v>
@@ -8658,7 +8645,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8668,7 +8655,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8692,6 +8679,220 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128624737</v>
+      </c>
+      <c r="B76" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>500373</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6759850</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128624738</v>
+      </c>
+      <c r="B77" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Flytarna S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>500888</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6760285</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38817-2025 artfynd.xlsx
+++ b/artfynd/A 38817-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AZ77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624740</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624741</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77629038</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495684</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495685</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495686</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1416,6 +1451,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495687</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495688</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1632,6 +1677,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495689</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1740,6 +1790,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495690</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1848,6 +1903,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495691</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495692</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128613125</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,6 +2245,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128613166</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2283,6 +2358,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624745</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2391,6 +2471,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624746</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2499,6 +2584,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624747</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2607,6 +2697,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624748</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2715,6 +2810,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624749</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2823,6 +2923,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624750</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2931,6 +3036,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624751</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3039,6 +3149,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624752</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3147,6 +3262,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624753</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3255,6 +3375,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624754</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3363,6 +3488,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624755</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3471,6 +3601,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624756</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3579,6 +3714,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624757</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3687,6 +3827,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624758</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3795,6 +3940,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624759</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3903,6 +4053,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624760</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4011,6 +4166,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624762</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4119,6 +4279,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624763</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4227,6 +4392,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624764</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4335,6 +4505,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624765</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4443,6 +4618,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624766</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4551,6 +4731,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624767</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4659,6 +4844,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624769</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4767,6 +4957,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624770</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4875,6 +5070,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624771</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4983,6 +5183,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624773</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5091,6 +5296,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624774</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5199,6 +5409,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624775</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5307,6 +5522,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624776</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5415,6 +5635,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624777</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5523,6 +5748,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624778</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5631,6 +5861,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624779</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5739,6 +5974,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624780</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5847,6 +6087,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624781</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5955,6 +6200,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624782</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6063,6 +6313,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624783</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6171,6 +6426,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624784</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6279,6 +6539,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624785</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6387,6 +6652,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624786</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6495,6 +6765,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624787</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6603,6 +6878,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624788</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6711,6 +6991,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624789</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6819,6 +7104,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624790</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6927,6 +7217,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624791</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7035,6 +7330,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624792</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7143,6 +7443,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624793</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7251,6 +7556,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624794</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7359,6 +7669,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624795</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7467,6 +7782,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624796</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7575,6 +7895,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128625716</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7682,6 +8007,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624739</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7802,6 +8132,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128495680</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7914,6 +8249,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612798</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8022,6 +8362,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624743</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8130,6 +8475,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624744</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8237,6 +8587,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624797</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8344,6 +8699,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624798</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8451,6 +8811,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624799</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8563,6 +8928,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128615890</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8679,6 +9049,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128613131</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8786,6 +9161,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624737</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8893,8 +9273,91 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624738</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>